--- a/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Apertura Barra Café" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cierre Cocina" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cierre Sala" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cierre Barra Café" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Barra Café" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Sala" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Barra Café" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura Cocina'!$A$1:$G$34</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Apertura Sala'!$A$1:$G$35</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Apertura Barra Café'!$A$1:$G$39</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Cierre Cocina'!$A$1:$G$33</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Cierre Sala'!$A$1:$G$33</definedName>
-    <definedName localSheetId="6" name="_xlnm.Print_Area">'Cierre Barra Café'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra Café'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra Café'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,11 @@
       <color rgb="00888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -146,50 +151,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -549,15 +570,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -565,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -572,6 +595,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -607,6 +631,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -614,8 +639,33 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -629,16 +679,16 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Cocina</t>
@@ -652,10 +702,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -680,7 +731,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -697,10 +748,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -726,10 +775,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -755,10 +802,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -784,10 +829,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -813,10 +856,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -849,10 +890,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -878,10 +917,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -907,10 +944,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -936,10 +971,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -965,10 +998,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -994,10 +1025,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -1023,10 +1052,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1059,10 +1086,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1088,10 +1113,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1117,10 +1140,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1146,10 +1167,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -1175,10 +1194,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1211,10 +1228,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1240,10 +1255,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -1269,10 +1282,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -1297,6 +1308,7 @@
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="C30" s="16" t="inlineStr">
         <is>
@@ -1305,14 +1317,19 @@
       </c>
       <c r="D30" s="17">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>de 20</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
@@ -1320,6 +1337,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -1338,8 +1356,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1353,16 +1381,16 @@
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Sala y Terraza</t>
@@ -1376,10 +1404,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1404,7 +1433,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1421,10 +1450,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1450,10 +1477,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1479,10 +1504,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1508,10 +1531,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1537,10 +1558,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -1566,10 +1585,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1595,10 +1612,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1631,10 +1646,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -1660,10 +1673,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -1689,10 +1700,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -1718,10 +1727,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -1747,10 +1754,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1783,10 +1788,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1812,10 +1815,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1841,10 +1842,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1870,10 +1869,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -1899,10 +1896,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1935,10 +1930,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1964,10 +1957,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -1993,10 +1984,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -2022,10 +2011,8 @@
       <c r="G28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="21" t="n">
+        <v>21</v>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
@@ -2050,6 +2037,7 @@
       <c r="F29" s="15" t="n"/>
       <c r="G29" s="15" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="C31" s="16" t="inlineStr">
         <is>
@@ -2058,14 +2046,19 @@
       </c>
       <c r="D31" s="17">
         <f>COUNTIF(F5:F29,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>de 21</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31">
+        <f>COUNTIF(B5:B29,"?*")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
@@ -2073,6 +2066,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
@@ -2084,15 +2078,25 @@
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2106,16 +2110,16 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Barra / Cafetería</t>
@@ -2129,10 +2133,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2157,7 +2162,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2174,10 +2179,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -2203,10 +2206,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -2232,10 +2233,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2261,10 +2260,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2290,10 +2287,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -2319,10 +2314,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -2355,10 +2348,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -2384,10 +2375,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2413,10 +2402,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2442,10 +2429,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -2471,10 +2456,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2500,10 +2483,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -2529,10 +2510,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2558,10 +2537,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>14</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -2594,10 +2571,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -2623,10 +2598,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -2652,10 +2625,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -2681,10 +2652,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>18</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -2710,10 +2679,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>19</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -2739,10 +2706,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>20</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -2775,10 +2740,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="21" t="n">
+        <v>21</v>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
@@ -2804,10 +2767,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="20" t="n">
+        <v>22</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -2833,10 +2794,8 @@
       <c r="G30" s="11" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="21" t="n">
+        <v>23</v>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
@@ -2862,10 +2821,8 @@
       <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="20" t="n">
+        <v>24</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -2891,10 +2848,8 @@
       <c r="G32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="21" t="n">
+        <v>25</v>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
@@ -2919,6 +2874,7 @@
       <c r="F33" s="15" t="n"/>
       <c r="G33" s="15" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="C35" s="16" t="inlineStr">
         <is>
@@ -2927,14 +2883,19 @@
       </c>
       <c r="D35" s="17">
         <f>COUNTIF(F5:F33,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>de 25</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F35">
+        <f>COUNTIF(B5:B33,"?*")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
@@ -2942,6 +2903,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
@@ -2956,12 +2918,22 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A21:G21"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G33">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F19 F20 F22 F23 F24 F25 F26 F27 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2975,16 +2947,16 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Cocina</t>
@@ -2998,10 +2970,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3026,7 +2999,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3043,10 +3016,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -3072,10 +3043,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -3101,10 +3070,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -3130,10 +3097,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -3159,10 +3124,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -3195,10 +3158,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -3224,10 +3185,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -3253,10 +3212,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -3282,10 +3239,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -3311,10 +3266,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -3340,10 +3293,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -3369,10 +3320,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -3405,10 +3354,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -3434,10 +3381,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -3463,10 +3408,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -3492,10 +3435,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -3528,10 +3469,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -3557,10 +3496,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -3586,10 +3523,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -3614,6 +3549,7 @@
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="C29" s="16" t="inlineStr">
         <is>
@@ -3622,14 +3558,19 @@
       </c>
       <c r="D29" s="17">
         <f>COUNTIF(F5:F27,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>de 19</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F29">
+        <f>COUNTIF(B5:B27,"?*")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -3637,6 +3578,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
@@ -3647,16 +3589,26 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3670,16 +3622,16 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Sala, Terraza y Caja</t>
@@ -3693,10 +3645,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3721,7 +3674,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3738,10 +3691,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -3767,10 +3718,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -3796,10 +3745,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -3825,10 +3772,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -3854,10 +3799,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -3890,10 +3833,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -3919,10 +3860,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -3948,10 +3887,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -3977,10 +3914,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -4006,10 +3941,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -4042,10 +3975,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -4071,10 +4002,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -4100,10 +4029,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -4129,10 +4056,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -4165,10 +4090,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -4194,10 +4117,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -4223,10 +4144,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -4252,10 +4171,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -4281,10 +4198,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -4309,6 +4224,7 @@
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="C29" s="16" t="inlineStr">
         <is>
@@ -4317,14 +4233,19 @@
       </c>
       <c r="D29" s="17">
         <f>COUNTIF(F5:F27,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>de 19</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F29">
+        <f>COUNTIF(B5:B27,"?*")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -4332,6 +4253,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
@@ -4342,16 +4264,26 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4365,16 +4297,16 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Barra / Cafetería</t>
@@ -4388,10 +4320,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4416,7 +4349,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -4433,10 +4366,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -4462,10 +4393,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -4491,10 +4420,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -4520,10 +4447,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -4549,10 +4474,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -4578,10 +4501,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -4614,10 +4535,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -4643,10 +4562,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -4672,10 +4589,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -4701,10 +4616,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -4737,10 +4650,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -4766,10 +4677,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -4795,10 +4704,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -4824,10 +4731,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -4853,10 +4758,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -4889,10 +4792,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -4918,10 +4819,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -4947,10 +4846,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -4976,10 +4873,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -5005,10 +4900,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -5033,6 +4926,7 @@
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="C30" s="16" t="inlineStr">
         <is>
@@ -5041,14 +4935,19 @@
       </c>
       <c r="D30" s="17">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>de 20</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
@@ -5056,6 +4955,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -5074,7 +4974,17 @@
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
@@ -16,11 +16,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Barra Café" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Apertura Barra Café'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra Café'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cierre Sala'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Cierre Barra Café'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra Café'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -674,7 +680,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1366,8 +1372,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1376,7 +1390,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2095,8 +2109,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2105,7 +2127,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2932,8 +2954,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2942,7 +2972,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3607,8 +3637,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3617,7 +3655,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4265,8 +4303,8 @@
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
@@ -4282,8 +4320,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4292,7 +4338,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4984,7 +5030,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/01-apertura-cierre.xlsx
@@ -16,18 +16,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Barra Café" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Apertura Barra Café'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra Café'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra Café'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cierre Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Cierre Barra Café'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra Café'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra Café'!$A$1:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,8 +101,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +147,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -159,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +221,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,86 +642,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas de Apertura y Cierre — Cafetería / Brunch</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists diarios para abrir y cerrar cada área de tu cafetería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Imprime una copia por día y área</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• El responsable de cada turno marca las tareas completadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• El encargado firma al final de cada turno</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>• Personaliza: borra tareas que no apliquen, añade las tuyas en las filas vacías</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>• Colores por zona: Cocina (verde), Sala/Terraza (azul), Barra Café (naranja)</t>
+      <c r="B9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra café).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 01-apertura-cierre.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -682,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -747,628 +895,875 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE PERSONAL</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido (gorro o redecilla)</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Sin anillos, reloj ni pulseras; uñas cortas, limpias y sin esmalte</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Lavado de manos al entrar y en cada cambio de tarea; lavamanos con jabón, papel y agua caliente</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Declarar síntomas digestivos o respiratorios: quien los tenga no manipula alimentos</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Encargado/a</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENCENDIDO DE EQUIPOS</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Encender horno y precalentar</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Encender la campana extractora y ventilar la cocina ANTES de encender nada más</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Encender plancha/grill para tostadas y brunch</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Si el local tiene gas: abrir la llave general y comprobar que NO huele a gas; si huele, no enciendas nada, ventila y avisa al mantenedor</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Encender campana extractora</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Encender el horno y precalentar para croissants, quiches y bollería</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Verificar cámaras frigoríficas: temperaturas OK</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Encender plancha/grill y tostadora para tostadas y brunch</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Encender baño maría (si aplica)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Comprobar que las cámaras frigoríficas han funcionado toda la noche y registrar temperatura (refrigeración 0-4 °C) — anota la lectura: ____ °C. Si hay desviación, no uses el género hasta valorarlo</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Cocinero apertura</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MISE EN PLACE BRUNCH</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Preparar masa de pancakes/tortitas</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Cortar pan para tostadas (sourdough, brioche, integral)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Preparar huevos: batidos para revueltos, pochados listos</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Preparar toppings: aguacate, tomate, salmón, bacon</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Montar bowls base: açaí, granola, fruta cortada</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Preparar salsas: hollandaise, pesto, hummus</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Preparar ensaladas y guarniciones del día</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y VERIFICACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de huevos, pan, aguacate, salmón</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de frutas frescas para bowls</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Preparar lista de pedidos urgentes</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Verificar caducidades de productos abiertos</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Comprobar que hay suficiente bacon/jamón para el día</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HIGIENE Y SEGURIDAD</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Lavarse las manos y colocarse uniforme completo</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+      <c r="G32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Comprobar que el botiquín y el extintor están accesibles y sin nada delante</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Verificar jabón y papel en dispensadores de cocina</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="30" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Desinfectar superficies de trabajo</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D30" s="17">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="n"/>
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="29" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="n"/>
+      <c r="B40" s="34" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="30" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D42" s="17">
+        <f>COUNTIFS(B5:B40,"?*",F5:F40,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30">
-        <f>COUNTIF(B5:B28,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="F42">
+        <f>COUNTIF(B5:B40,"?*")-COUNTIF(F5:F40,"N/A")</f>
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G28">
+  <conditionalFormatting sqref="A5:G40">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F27 F28 F29 F30 F31 F33 F34 F35 F36 F37 F38 F39 F40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1392,7 +1787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1457,655 +1852,726 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA INTERIOR</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Encender luces y climatización</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Limpiar y montar mesas: manteles/salvamanteles, cubiertos</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Colocar menús/cartas en mesas</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Verificar que las sillas están limpias y alineadas</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Actualizar pizarra del día (platos, especiales, precio brunch)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Poner música ambiental a volumen adecuado</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Verificar iluminación cálida (no fluorescente)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  TERRAZA</t>
         </is>
       </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Sacar mesas y sillas de terraza</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Limpiar mesas y sillas de terraza</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Abrir sombrillas/toldos si hace sol</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Colocar macetas/decoración si aplica</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Verificar ceniceros limpios (zona fumadores)</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTACIONES DE SERVICIO</t>
         </is>
       </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Reponer servilletas, azúcar, sacarina, palillos</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de salsas (kétchup, mostaza, tabasco)</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Reponer pajitas de papel y agitadores</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Camarero/a apertura</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Verificar TPV/datáfono: cargado y funcionando</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Preparar fondo de caja</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA RÁPIDA</t>
         </is>
       </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Barrer y fregar suelo de sala</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Limpiar cristales de entrada</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Limpiar baños: jabón, papel, ambientador</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="n">
+      <c r="A29" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>Vaciar papeleras</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-    </row>
-    <row r="30"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
     <row r="31">
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D31" s="17">
-        <f>COUNTIF(F5:F29,"✓")</f>
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="30" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D36" s="17">
+        <f>COUNTIFS(B5:B34,"?*",F5:F34,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F31">
-        <f>COUNTIF(B5:B29,"?*")</f>
+      <c r="F36">
+        <f>COUNTIF(B5:B34,"?*")-COUNTIF(F5:F34,"N/A")</f>
         <v>21.0</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G29">
+  <conditionalFormatting sqref="A5:G34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2129,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2194,763 +2660,834 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÁQUINA DE ESPRESSO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Encender máquina de espresso (15-20 min calentamiento)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>06:45</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Purgar grupo: dejar correr agua 5 segundos por cada grupo</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Calibrar molienda: extraer shot de prueba (25-30s, 25-30ml)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Verificar presión de la máquina (9 bar)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Limpiar portafiltros y secar bien</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Verificar lance de vapor: purgar y limpiar</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK BARRA</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de café en grano (bolsa abierta + reserva)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de leches: entera, desnatada, avena, soja, almendra</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de cacao en polvo y canela</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de siropes: vainilla, caramelo, avellana</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de té e infusiones (variedades)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de zumos naturales / zumo de naranja</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de azúcar blanco, moreno, sacarina, estevia</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de vasos take-away, tapas, portavasos</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN BARRA</t>
         </is>
       </c>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Preparar jarritas de leche fría (entera + vegetal)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Preparar hielo (cubitera llena)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Montar estación de toppings: cacao, canela, siropes</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Preparar batch brew / café filtro del día</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Llenar termos de agua caliente para tés</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Preparar smoothies base si aplica</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  VITRINA Y PASTELERÍA</t>
         </is>
       </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="26" t="n"/>
+      <c r="G28" s="26" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="n">
+      <c r="A29" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>Limpiar cristal de vitrina interior y exterior</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="n">
+      <c r="A30" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Reponer vitrina con bollería del día</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="n">
+      <c r="A31" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>Etiquetar precios y alérgenos en vitrina</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Verificar temperatura de vitrina refrigerada</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>Verificar temperatura de vitrina refrigerada (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n">
+      <c r="A33" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>Colocar pinzas/guantes para servir</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
-    </row>
-    <row r="34"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="30" t="n"/>
+    </row>
     <row r="35">
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D35" s="17">
-        <f>COUNTIF(F5:F33,"✓")</f>
+      <c r="A35" s="33" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D40" s="17">
+        <f>COUNTIFS(B5:B38,"?*",F5:F38,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F35">
-        <f>COUNTIF(B5:B33,"?*")</f>
+      <c r="F40">
+        <f>COUNTIF(B5:B38,"?*")-COUNTIF(F5:F38,"N/A")</f>
         <v>25.0</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G33">
+  <conditionalFormatting sqref="A5:G38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F19 F20 F22 F23 F24 F25 F26 F27 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F19 F20 F22 F23 F24 F25 F26 F27 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2974,7 +3511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3039,601 +3576,672 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONSERVACIÓN DE PRODUCTO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Etiquetar y fechar todas las pre-elaboraciones</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Guardar salsas en recipientes herméticos con fecha</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar toppings de brunch</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Guardar pan sobrante en bolsa hermética</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Congelar lo que no se usará mañana (etiquetar)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar plancha/grill</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Limpiar horno (interior si toca)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Limpiar superficies de trabajo y tablas de corte</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Fregar y secar utensilios</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Vaciar y limpiar freidora (si aplica)</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Vaciar y limpiar la freidora (si aplica): manipular el aceite SÓLO por debajo de 40 °C, nunca en caliente, con guantes y recipiente estable; el aceite usado, al bidón del gestor autorizado</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Barrer y fregar suelo de cocina</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Sacar basura y reciclar</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS Y SEGURIDAD</t>
         </is>
       </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Apagar horno, plancha, campana</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Verificar que cámaras están cerradas y a temperatura</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Verificar que cámaras están cerradas y a temperatura (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Cerrar llave de gas (si aplica)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Apagar luces de cocina</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN PARA MAÑANA</t>
         </is>
       </c>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Descongelar lo necesario para mañana (pasar a cámara)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Anotar faltantes para pedido de mañana</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Preparar lista de mise en place del día siguiente</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
     <row r="29">
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D29" s="17">
-        <f>COUNTIF(F5:F27,"✓")</f>
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="17">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F29">
-        <f>COUNTIF(B5:B27,"?*")</f>
+      <c r="F34">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
         <v>19.0</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G27">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3657,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3722,601 +4330,672 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y MOBILIARIO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Desmontar mesas: recoger manteles, cubiertos, vasos</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Limpiar todas las mesas con desinfectante</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Alinear sillas y mesas</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Barrer suelo de sala</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Fregar suelo de sala</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  TERRAZA</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Recoger mesas y sillas de terraza (o apilar y encadenar)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Cerrar sombrillas/toldos</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Limpiar zona de terraza</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Recoger ceniceros y vaciar</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Guardar decoración exterior si llueve</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTACIONES Y BAÑOS</t>
         </is>
       </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Reponer servilletas, azúcar, salsas para mañana</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Limpiar estación de servicio</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Camarero/a cierre</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Limpieza final de baños: jabón, papel, suelo</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Vaciar todas las papeleras</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CAJA Y CIERRE</t>
         </is>
       </c>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Cuadrar caja del día</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Revisar propinas del equipo</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Anotar incidencias del día</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Apagar música, climatización, luces</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Activar alarma y cerrar con llave</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
     <row r="29">
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D29" s="17">
-        <f>COUNTIF(F5:F27,"✓")</f>
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="17">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F29">
-        <f>COUNTIF(B5:B27,"?*")</f>
+      <c r="F34">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
         <v>19.0</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G27">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4340,7 +5019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4405,628 +5084,699 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÁQUINA DE ESPRESSO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Backflush con pastilla de limpieza (cada grupo)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Limpiar portafiltros con agua caliente</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Purgar lanza de vapor y limpiar con paño húmedo</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Limpiar bandeja de goteo</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Vaciar posos del cajón de borra</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Apagar máquina de espresso</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOLINILLO Y EQUIPOS</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Limpiar molinillo: retirar café residual con cepillo</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Cerrar tolva del molinillo</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Limpiar batidora/blender de smoothies</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Vaciar y limpiar termos de café filtro</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y VITRINA</t>
         </is>
       </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Guardar bollería sobrante (etiquetar con fecha)</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Cubrir vitrina o vaciar si es refrigerada</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Guardar leches abiertas en cámara</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Anotar stock de café en grano restante</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Anotar pedidos necesarios para mañana (leche, café, etc.)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA BARRA</t>
         </is>
       </c>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar superficie de barra</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Limpiar cristal de vitrina</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Lavar y secar jarritas de leche</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Vaciar cubitera de hielo</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Barrer zona de barra</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
     <row r="30">
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D30" s="17">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D35" s="17">
+        <f>COUNTIFS(B5:B33,"?*",F5:F33,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30">
-        <f>COUNTIF(B5:B28,"?*")</f>
+      <c r="F35">
+        <f>COUNTIF(B5:B33,"?*")-COUNTIF(F5:F33,"N/A")</f>
         <v>20.0</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G28">
+  <conditionalFormatting sqref="A5:G33">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
